--- a/product_selector_out/STM32U5F7-5G7.xlsx
+++ b/product_selector_out/STM32U5F7-5G7.xlsx
@@ -2470,9 +2470,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="9" t="inlineStr">
@@ -2797,9 +2797,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -2893,7 +2893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 32. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 72. Typical dynamic current consumption of peripherals</t>
+          <t>Table 32. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32U5G7VJ</t>
+          <t>STM32U5F7VJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 72. Typical dynamic current consumption of peripherals</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 20. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -3086,15 +3086,59 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32U5G7VJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 33. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32U5G7VJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Table 73. Typical dynamic current consumption of peripherals</t>
         </is>

--- a/product_selector_out/STM32U5F7-5G7.xlsx
+++ b/product_selector_out/STM32U5F7-5G7.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM13"/>
+  <dimension ref="A1:BN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5f7vj.pdf</t>
         </is>
       </c>
@@ -1641,12 +1653,17 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u5g7vj.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -1667,16 +1684,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -1689,6 +1704,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -1708,7 +1724,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -1727,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM13"/>
+  <dimension ref="A1:BN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1795,6 +1813,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2128,6 +2147,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -2223,6 +2247,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2545,7 +2570,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2872,7 +2902,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -2880,8 +2915,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
